--- a/public/exports-60-250-with-coowners/29189501.xlsx
+++ b/public/exports-60-250-with-coowners/29189501.xlsx
@@ -2464,12 +2464,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311158150</t>
+          <t xml:space="preserve">311158100</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knud Erik Møllers Tegnestue</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311158156</t>
+          <t xml:space="preserve">311158108</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knud Erik Møllers Tegnestue</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M35" t="inlineStr">
